--- a/錢塘潮選股報告_2026-09-12.xlsx
+++ b/錢塘潮選股報告_2026-09-12.xlsx
@@ -486,42 +486,42 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>2812</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>59.4</v>
+        <v>19.5</v>
       </c>
       <c r="C3" t="n">
-        <v>79008</v>
+        <v>28752</v>
       </c>
       <c r="D3" t="n">
         <v>4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>F1_主力大買、F2_一朵花、F3_主外上輕、F5_洗盤後</t>
+          <t>F1_主力大買、F2_一朵花、F5_洗盤後、F7_筆張現形</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2812</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19.5</v>
+        <v>59.4</v>
       </c>
       <c r="C4" t="n">
-        <v>28752</v>
+        <v>79008</v>
       </c>
       <c r="D4" t="n">
         <v>4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>F1_主力大買、F2_一朵花、F5_洗盤後、F7_筆張現形</t>
+          <t>F1_主力大買、F2_一朵花、F3_主外上輕、F5_洗盤後</t>
         </is>
       </c>
     </row>
@@ -549,35 +549,35 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>5876</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>82.5</v>
+        <v>48.65</v>
       </c>
       <c r="C6" t="n">
-        <v>1065</v>
+        <v>6954</v>
       </c>
       <c r="D6" t="n">
         <v>3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>F3_主外上輕、F5_洗盤後、F7_筆張現形</t>
+          <t>F1_主力大買、F2_一朵花、F3_主外上輕</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5876</t>
+          <t>2845</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>48.65</v>
+        <v>13.7</v>
       </c>
       <c r="C7" t="n">
-        <v>6954</v>
+        <v>11328</v>
       </c>
       <c r="D7" t="n">
         <v>3</v>
@@ -591,63 +591,63 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2845</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13.7</v>
+        <v>82.5</v>
       </c>
       <c r="C8" t="n">
-        <v>11328</v>
+        <v>1065</v>
       </c>
       <c r="D8" t="n">
         <v>3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>F1_主力大買、F2_一朵花、F3_主外上輕</t>
+          <t>F3_主外上輕、F5_洗盤後、F7_筆張現形</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>2834</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>35.3</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>5207</v>
+        <v>38566</v>
       </c>
       <c r="D9" t="n">
         <v>2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>F1_主力大買、F3_主外上輕</t>
+          <t>F2_一朵花、F3_主外上輕</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2834</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18</v>
+        <v>115.5</v>
       </c>
       <c r="C10" t="n">
-        <v>38566</v>
+        <v>1879</v>
       </c>
       <c r="D10" t="n">
         <v>2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>F2_一朵花、F3_主外上輕</t>
+          <t>F3_主外上輕、F5_洗盤後</t>
         </is>
       </c>
     </row>
@@ -675,161 +675,161 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2409</t>
+          <t>2354</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>30.2</v>
+        <v>65.7</v>
       </c>
       <c r="C12" t="n">
-        <v>517956</v>
+        <v>17964</v>
       </c>
       <c r="D12" t="n">
         <v>2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>F2_一朵花、F3_主外上輕</t>
+          <t>F1_主力大買、F2_一朵花</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>508</v>
+        <v>35.3</v>
       </c>
       <c r="C13" t="n">
-        <v>2573</v>
+        <v>5207</v>
       </c>
       <c r="D13" t="n">
         <v>2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>F3_主外上輕、F5_洗盤後</t>
+          <t>F1_主力大買、F3_主外上輕</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>2409</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>115.5</v>
+        <v>30.2</v>
       </c>
       <c r="C14" t="n">
-        <v>1879</v>
+        <v>517956</v>
       </c>
       <c r="D14" t="n">
         <v>2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>F3_主外上輕、F5_洗盤後</t>
+          <t>F2_一朵花、F3_主外上輕</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2354</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>65.7</v>
+        <v>508</v>
       </c>
       <c r="C15" t="n">
-        <v>17964</v>
+        <v>2573</v>
       </c>
       <c r="D15" t="n">
         <v>2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>F1_主力大買、F2_一朵花</t>
+          <t>F3_主外上輕、F5_洗盤後</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>988</v>
+        <v>89</v>
       </c>
       <c r="C16" t="n">
-        <v>3847</v>
+        <v>2460</v>
       </c>
       <c r="D16" t="n">
         <v>1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>F3_主外上輕</t>
+          <t>F7_筆張現形</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>89</v>
+        <v>6120</v>
       </c>
       <c r="C17" t="n">
-        <v>2460</v>
+        <v>1425</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>F7_筆張現形</t>
+          <t>F3_主外上輕</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1060</v>
+        <v>495</v>
       </c>
       <c r="C18" t="n">
-        <v>10593</v>
+        <v>18333</v>
       </c>
       <c r="D18" t="n">
         <v>1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>F3_主外上輕</t>
+          <t>F1_主力大買</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>7799</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6120</v>
+        <v>414.5</v>
       </c>
       <c r="C19" t="n">
-        <v>1425</v>
+        <v>1280</v>
       </c>
       <c r="D19" t="n">
         <v>1</v>
@@ -843,35 +843,35 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>495</v>
+        <v>988</v>
       </c>
       <c r="C20" t="n">
-        <v>18333</v>
+        <v>3847</v>
       </c>
       <c r="D20" t="n">
         <v>1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>F1_主力大買</t>
+          <t>F3_主外上輕</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>7799</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>414.5</v>
+        <v>1060</v>
       </c>
       <c r="C21" t="n">
-        <v>1280</v>
+        <v>10593</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -916,118 +916,118 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2801</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>27.9</v>
+        <v>42.35</v>
       </c>
       <c r="C2" t="n">
-        <v>37867</v>
+        <v>17009</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>2812</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>35.3</v>
+        <v>19.5</v>
       </c>
       <c r="C3" t="n">
-        <v>5207</v>
+        <v>28752</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2845</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13.7</v>
+        <v>35.3</v>
       </c>
       <c r="C4" t="n">
-        <v>11328</v>
+        <v>5207</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5876</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>48.65</v>
+        <v>59.4</v>
       </c>
       <c r="C5" t="n">
-        <v>6954</v>
+        <v>79008</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2354</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>65.7</v>
+        <v>495</v>
       </c>
       <c r="C6" t="n">
-        <v>17964</v>
+        <v>18333</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>2801</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>59.4</v>
+        <v>27.9</v>
       </c>
       <c r="C7" t="n">
-        <v>79008</v>
+        <v>37867</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2812</t>
+          <t>2354</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>19.5</v>
+        <v>65.7</v>
       </c>
       <c r="C8" t="n">
-        <v>28752</v>
+        <v>17964</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>5876</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>495</v>
+        <v>48.65</v>
       </c>
       <c r="C9" t="n">
-        <v>18333</v>
+        <v>6954</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2845</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>42.35</v>
+        <v>13.7</v>
       </c>
       <c r="C10" t="n">
-        <v>17009</v>
+        <v>11328</v>
       </c>
     </row>
   </sheetData>
@@ -1064,118 +1064,118 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2845</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13.7</v>
+        <v>42.35</v>
       </c>
       <c r="C2" t="n">
-        <v>11328</v>
+        <v>17009</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2409</t>
+          <t>2834</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>30.2</v>
+        <v>18</v>
       </c>
       <c r="C3" t="n">
-        <v>517956</v>
+        <v>38566</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5876</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>48.65</v>
+        <v>106.5</v>
       </c>
       <c r="C4" t="n">
-        <v>6954</v>
+        <v>7845</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2354</t>
+          <t>2812</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>65.7</v>
+        <v>19.5</v>
       </c>
       <c r="C5" t="n">
-        <v>17964</v>
+        <v>28752</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2834</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18</v>
+        <v>59.4</v>
       </c>
       <c r="C6" t="n">
-        <v>38566</v>
+        <v>79008</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>2354</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>106.5</v>
+        <v>65.7</v>
       </c>
       <c r="C7" t="n">
-        <v>7845</v>
+        <v>17964</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>2409</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>59.4</v>
+        <v>30.2</v>
       </c>
       <c r="C8" t="n">
-        <v>79008</v>
+        <v>517956</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2812</t>
+          <t>5876</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>19.5</v>
+        <v>48.65</v>
       </c>
       <c r="C9" t="n">
-        <v>28752</v>
+        <v>6954</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2845</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>42.35</v>
+        <v>13.7</v>
       </c>
       <c r="C10" t="n">
-        <v>17009</v>
+        <v>11328</v>
       </c>
     </row>
   </sheetData>
@@ -1212,66 +1212,66 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2801</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>27.9</v>
+        <v>42.35</v>
       </c>
       <c r="C2" t="n">
-        <v>37867</v>
+        <v>17009</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>2834</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>988</v>
+        <v>18</v>
       </c>
       <c r="C3" t="n">
-        <v>3847</v>
+        <v>38566</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>35.3</v>
+        <v>106.5</v>
       </c>
       <c r="C4" t="n">
-        <v>5207</v>
+        <v>7845</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>508</v>
+        <v>35.3</v>
       </c>
       <c r="C5" t="n">
-        <v>2573</v>
+        <v>5207</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2845</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13.7</v>
+        <v>59.4</v>
       </c>
       <c r="C6" t="n">
-        <v>11328</v>
+        <v>79008</v>
       </c>
     </row>
     <row r="7">
@@ -1290,131 +1290,131 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2409</t>
+          <t>7799</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>30.2</v>
+        <v>414.5</v>
       </c>
       <c r="C8" t="n">
-        <v>517956</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>2801</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>115.5</v>
+        <v>27.9</v>
       </c>
       <c r="C9" t="n">
-        <v>1879</v>
+        <v>37867</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>5876</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>48.65</v>
+        <v>82.5</v>
       </c>
       <c r="C10" t="n">
-        <v>6954</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1060</v>
+        <v>988</v>
       </c>
       <c r="C11" t="n">
-        <v>10593</v>
+        <v>3847</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2834</t>
+          <t>2409</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>30.2</v>
       </c>
       <c r="C12" t="n">
-        <v>38566</v>
+        <v>517956</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>5876</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>106.5</v>
+        <v>48.65</v>
       </c>
       <c r="C13" t="n">
-        <v>7845</v>
+        <v>6954</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>82.5</v>
+        <v>508</v>
       </c>
       <c r="C14" t="n">
-        <v>1065</v>
+        <v>2573</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>59.4</v>
+        <v>115.5</v>
       </c>
       <c r="C15" t="n">
-        <v>79008</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>42.35</v>
+        <v>1060</v>
       </c>
       <c r="C16" t="n">
-        <v>17009</v>
+        <v>10593</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>7799</t>
+          <t>2845</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>414.5</v>
+        <v>13.7</v>
       </c>
       <c r="C17" t="n">
-        <v>1280</v>
+        <v>11328</v>
       </c>
     </row>
   </sheetData>
@@ -1482,79 +1482,79 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>508</v>
+        <v>42.35</v>
       </c>
       <c r="C2" t="n">
-        <v>2573</v>
+        <v>17009</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>2812</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>115.5</v>
+        <v>19.5</v>
       </c>
       <c r="C3" t="n">
-        <v>1879</v>
+        <v>28752</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>82.5</v>
+        <v>59.4</v>
       </c>
       <c r="C4" t="n">
-        <v>1065</v>
+        <v>79008</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>59.4</v>
+        <v>82.5</v>
       </c>
       <c r="C5" t="n">
-        <v>79008</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2812</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19.5</v>
+        <v>508</v>
       </c>
       <c r="C6" t="n">
-        <v>28752</v>
+        <v>2573</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>42.35</v>
+        <v>115.5</v>
       </c>
       <c r="C7" t="n">
-        <v>17009</v>
+        <v>1879</v>
       </c>
     </row>
   </sheetData>
@@ -1635,40 +1635,40 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2801</t>
+          <t>2812</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>27.9</v>
+        <v>19.5</v>
       </c>
       <c r="C3" t="n">
-        <v>37867</v>
+        <v>28752</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2801</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>82.5</v>
+        <v>27.9</v>
       </c>
       <c r="C4" t="n">
-        <v>1065</v>
+        <v>37867</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2812</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19.5</v>
+        <v>82.5</v>
       </c>
       <c r="C5" t="n">
-        <v>28752</v>
+        <v>1065</v>
       </c>
     </row>
   </sheetData>
